--- a/installer/modelos/modelo-cadastro-de-cartoes.xlsx
+++ b/installer/modelos/modelo-cadastro-de-cartoes.xlsx
@@ -25808,11 +25808,6 @@
           <t>SOCIAL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Maria Exemplo</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>ATIVO</t>
